--- a/data/weapons.xlsx
+++ b/data/weapons.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="weapons" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>weaponId</t>
   </si>
@@ -83,16 +88,34 @@
     <t>(默认值行)</t>
   </si>
   <si>
-    <t>手枪</t>
-  </si>
-  <si>
-    <t>基础手枪，攻击力低但射速稳定</t>
-  </si>
-  <si>
-    <t>步枪</t>
-  </si>
-  <si>
-    <t>伤害更高，射速略慢</t>
+    <t>小木杖</t>
+  </si>
+  <si>
+    <t>最基础的法杖，可以略微增加伤害</t>
+  </si>
+  <si>
+    <t>学徒法杖</t>
+  </si>
+  <si>
+    <t>学徒使用的法杖，可以增强一些法术</t>
+  </si>
+  <si>
+    <t>法师杖</t>
+  </si>
+  <si>
+    <t>使用稀有材料制作的进阶法杖，通常正式法师才能使用</t>
+  </si>
+  <si>
+    <t>魔杖</t>
+  </si>
+  <si>
+    <t>镶嵌了魔石的发张给，可以大幅增强法术</t>
+  </si>
+  <si>
+    <t>奥数魔杖</t>
+  </si>
+  <si>
+    <t>使用先进工艺制作的魔杖，可以提升吟唱速度，也有不错的伤害增幅</t>
   </si>
 </sst>
 </file>
@@ -1237,8 +1260,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="60.5555555555556" customWidth="1"/>
+    <col min="4" max="4" width="15.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="29.4444444444444" customWidth="1"/>
+    <col min="6" max="6" width="24.4444444444444" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -1357,9 +1387,69 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>1.75</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>2.25</v>
+      </c>
+      <c r="F9">
         <v>0</v>
       </c>
     </row>

--- a/data/weapons.xlsx
+++ b/data/weapons.xlsx
@@ -1264,7 +1264,7 @@
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="60.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="64" customWidth="1"/>
     <col min="4" max="4" width="15.3333333333333" customWidth="1"/>
     <col min="5" max="5" width="29.4444444444444" customWidth="1"/>
     <col min="6" max="6" width="24.4444444444444" customWidth="1"/>
